--- a/DataAnalysis/TryingToPackStuffBetter/PreprocessingADV/LC/0.3/Results.xlsx
+++ b/DataAnalysis/TryingToPackStuffBetter/PreprocessingADV/LC/0.3/Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\LC\0.3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\TryingToPackStuffBetter\PreprocessingADV\LC\0.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3090B87-9301-41AE-922E-724B564B3639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB90FEBE-5959-45BF-A09E-057B675021D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -140,8 +140,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -461,34 +462,34 @@
       <c r="A2" t="s">
         <v>16</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>12.75</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>1.2076147288491199</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>14.2</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>2.964606025914553</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>16.7</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>2.9173808649388069</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>14.550000000000002</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>1.224870867469428</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
         <v>2.7999999999999994</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>1.0387551904462469</v>
       </c>
     </row>
@@ -496,34 +497,34 @@
       <c r="A3" t="s">
         <v>20</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>13.9</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>2.7018512172212614</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>16.2</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>1.0368220676663862</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>18.2</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>1.6431676725154982</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>16.100000000000001</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>0.85472542699720599</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>2.8</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>1.1571036638473178</v>
       </c>
     </row>
@@ -531,34 +532,34 @@
       <c r="A4" t="s">
         <v>21</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>13</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>2.6692695630078278</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>14</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>1.8371173070873836</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>16.2</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>5.1063685726747137</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>14.4</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>2.6209625034411439</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>2.2999999999999998</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>1.6641647888488822</v>
       </c>
     </row>
